--- a/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - October-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - October-2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\ECE (ROSE)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F448BC5-6B02-406E-8BBE-38BBCFE3979F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433487CE-19D3-4101-88F5-87A4782D2C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE (ROSE)" sheetId="2" r:id="rId1"/>
@@ -638,6 +638,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -649,15 +658,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -712,6 +712,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -723,24 +733,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1068,86 +1068,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
       <c r="AK1" s="19"/>
       <c r="AL1" s="19"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="21"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="21"/>
       <c r="AK2" s="18"/>
       <c r="AL2" s="18"/>
       <c r="AM2" s="18"/>
@@ -1292,16 +1292,16 @@
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="24" t="s">
+      <c r="AK3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="24" t="s">
+      <c r="AL3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="21" t="s">
+      <c r="AM3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="23"/>
+      <c r="AN3" s="26"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
@@ -1404,8 +1404,8 @@
       <c r="AJ4" s="16">
         <v>45596</v>
       </c>
-      <c r="AK4" s="24"/>
-      <c r="AL4" s="24"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1444,7 +1444,7 @@
       <c r="J5" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="23" t="s">
         <v>118</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -1465,7 +1465,7 @@
       <c r="Q5" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R5" s="27" t="s">
+      <c r="R5" s="23" t="s">
         <v>118</v>
       </c>
       <c r="S5" s="8" t="s">
@@ -1486,7 +1486,7 @@
       <c r="X5" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y5" s="27" t="s">
+      <c r="Y5" s="23" t="s">
         <v>118</v>
       </c>
       <c r="Z5" s="8" t="s">
@@ -1507,7 +1507,7 @@
       <c r="AE5" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF5" s="27" t="s">
+      <c r="AF5" s="23" t="s">
         <v>118</v>
       </c>
       <c r="AG5" s="8" t="s">
@@ -1570,7 +1570,7 @@
       <c r="J6" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K6" s="27"/>
+      <c r="K6" s="23"/>
       <c r="L6" s="8" t="s">
         <v>120</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="Q6" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R6" s="27"/>
+      <c r="R6" s="23"/>
       <c r="S6" s="8" t="s">
         <v>120</v>
       </c>
@@ -1608,7 +1608,7 @@
       <c r="X6" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y6" s="27"/>
+      <c r="Y6" s="23"/>
       <c r="Z6" s="8" t="s">
         <v>121</v>
       </c>
@@ -1627,7 +1627,7 @@
       <c r="AE6" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF6" s="27"/>
+      <c r="AF6" s="23"/>
       <c r="AG6" s="8" t="s">
         <v>120</v>
       </c>
@@ -1686,7 +1686,7 @@
       <c r="J7" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K7" s="27"/>
+      <c r="K7" s="23"/>
       <c r="L7" s="8" t="s">
         <v>120</v>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="Q7" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R7" s="27"/>
+      <c r="R7" s="23"/>
       <c r="S7" s="8" t="s">
         <v>120</v>
       </c>
@@ -1724,7 +1724,7 @@
       <c r="X7" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y7" s="27"/>
+      <c r="Y7" s="23"/>
       <c r="Z7" s="8" t="s">
         <v>120</v>
       </c>
@@ -1743,7 +1743,7 @@
       <c r="AE7" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF7" s="27"/>
+      <c r="AF7" s="23"/>
       <c r="AG7" s="8" t="s">
         <v>120</v>
       </c>
@@ -1800,7 +1800,7 @@
       <c r="J8" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="23"/>
       <c r="L8" s="8" t="s">
         <v>120</v>
       </c>
@@ -1819,7 +1819,7 @@
       <c r="Q8" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R8" s="27"/>
+      <c r="R8" s="23"/>
       <c r="S8" s="8" t="s">
         <v>120</v>
       </c>
@@ -1838,7 +1838,7 @@
       <c r="X8" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y8" s="27"/>
+      <c r="Y8" s="23"/>
       <c r="Z8" s="8" t="s">
         <v>120</v>
       </c>
@@ -1857,7 +1857,7 @@
       <c r="AE8" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF8" s="27"/>
+      <c r="AF8" s="23"/>
       <c r="AG8" s="8" t="s">
         <v>120</v>
       </c>
@@ -1878,12 +1878,12 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="AM8" s="21" t="s">
+      <c r="AM8" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="22"/>
-      <c r="AO8" s="22"/>
-      <c r="AP8" s="23"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="25"/>
+      <c r="AP8" s="26"/>
     </row>
     <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -1916,7 +1916,7 @@
       <c r="J9" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K9" s="27"/>
+      <c r="K9" s="23"/>
       <c r="L9" s="8" t="s">
         <v>120</v>
       </c>
@@ -1935,7 +1935,7 @@
       <c r="Q9" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R9" s="27"/>
+      <c r="R9" s="23"/>
       <c r="S9" s="8" t="s">
         <v>120</v>
       </c>
@@ -1954,7 +1954,7 @@
       <c r="X9" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y9" s="27"/>
+      <c r="Y9" s="23"/>
       <c r="Z9" s="8" t="s">
         <v>120</v>
       </c>
@@ -1973,7 +1973,7 @@
       <c r="AE9" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF9" s="27"/>
+      <c r="AF9" s="23"/>
       <c r="AG9" s="8" t="s">
         <v>120</v>
       </c>
@@ -2038,7 +2038,7 @@
       <c r="J10" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K10" s="27"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="8" t="s">
         <v>120</v>
       </c>
@@ -2057,7 +2057,7 @@
       <c r="Q10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R10" s="27"/>
+      <c r="R10" s="23"/>
       <c r="S10" s="8" t="s">
         <v>120</v>
       </c>
@@ -2076,7 +2076,7 @@
       <c r="X10" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y10" s="27"/>
+      <c r="Y10" s="23"/>
       <c r="Z10" s="8" t="s">
         <v>120</v>
       </c>
@@ -2095,7 +2095,7 @@
       <c r="AE10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF10" s="27"/>
+      <c r="AF10" s="23"/>
       <c r="AG10" s="8" t="s">
         <v>120</v>
       </c>
@@ -2163,7 +2163,7 @@
       <c r="J11" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="23"/>
       <c r="L11" s="8" t="s">
         <v>120</v>
       </c>
@@ -2182,7 +2182,7 @@
       <c r="Q11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R11" s="27"/>
+      <c r="R11" s="23"/>
       <c r="S11" s="8" t="s">
         <v>120</v>
       </c>
@@ -2201,7 +2201,7 @@
       <c r="X11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y11" s="27"/>
+      <c r="Y11" s="23"/>
       <c r="Z11" s="8" t="s">
         <v>120</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="AE11" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF11" s="27"/>
+      <c r="AF11" s="23"/>
       <c r="AG11" s="8" t="s">
         <v>121</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="J12" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K12" s="27"/>
+      <c r="K12" s="23"/>
       <c r="L12" s="8" t="s">
         <v>120</v>
       </c>
@@ -2305,7 +2305,7 @@
       <c r="Q12" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R12" s="27"/>
+      <c r="R12" s="23"/>
       <c r="S12" s="8" t="s">
         <v>121</v>
       </c>
@@ -2324,7 +2324,7 @@
       <c r="X12" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y12" s="27"/>
+      <c r="Y12" s="23"/>
       <c r="Z12" s="8" t="s">
         <v>120</v>
       </c>
@@ -2343,7 +2343,7 @@
       <c r="AE12" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF12" s="27"/>
+      <c r="AF12" s="23"/>
       <c r="AG12" s="8" t="s">
         <v>120</v>
       </c>
@@ -2411,7 +2411,7 @@
       <c r="J13" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K13" s="27"/>
+      <c r="K13" s="23"/>
       <c r="L13" s="8" t="s">
         <v>120</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="Q13" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R13" s="27"/>
+      <c r="R13" s="23"/>
       <c r="S13" s="8" t="s">
         <v>120</v>
       </c>
@@ -2449,7 +2449,7 @@
       <c r="X13" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y13" s="27"/>
+      <c r="Y13" s="23"/>
       <c r="Z13" s="8" t="s">
         <v>120</v>
       </c>
@@ -2468,7 +2468,7 @@
       <c r="AE13" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF13" s="27"/>
+      <c r="AF13" s="23"/>
       <c r="AG13" s="8" t="s">
         <v>120</v>
       </c>
@@ -2525,7 +2525,7 @@
       <c r="J14" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="23"/>
       <c r="L14" s="8" t="s">
         <v>120</v>
       </c>
@@ -2544,7 +2544,7 @@
       <c r="Q14" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R14" s="27"/>
+      <c r="R14" s="23"/>
       <c r="S14" s="8" t="s">
         <v>120</v>
       </c>
@@ -2563,7 +2563,7 @@
       <c r="X14" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y14" s="27"/>
+      <c r="Y14" s="23"/>
       <c r="Z14" s="8" t="s">
         <v>120</v>
       </c>
@@ -2582,7 +2582,7 @@
       <c r="AE14" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF14" s="27"/>
+      <c r="AF14" s="23"/>
       <c r="AG14" s="8" t="s">
         <v>120</v>
       </c>
@@ -2639,7 +2639,7 @@
       <c r="J15" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K15" s="27"/>
+      <c r="K15" s="23"/>
       <c r="L15" s="8" t="s">
         <v>120</v>
       </c>
@@ -2658,7 +2658,7 @@
       <c r="Q15" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R15" s="27"/>
+      <c r="R15" s="23"/>
       <c r="S15" s="8" t="s">
         <v>120</v>
       </c>
@@ -2677,7 +2677,7 @@
       <c r="X15" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y15" s="27"/>
+      <c r="Y15" s="23"/>
       <c r="Z15" s="8" t="s">
         <v>120</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="AE15" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF15" s="27"/>
+      <c r="AF15" s="23"/>
       <c r="AG15" s="8" t="s">
         <v>120</v>
       </c>
@@ -2753,7 +2753,7 @@
       <c r="J16" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K16" s="27"/>
+      <c r="K16" s="23"/>
       <c r="L16" s="8" t="s">
         <v>120</v>
       </c>
@@ -2772,7 +2772,7 @@
       <c r="Q16" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R16" s="27"/>
+      <c r="R16" s="23"/>
       <c r="S16" s="8" t="s">
         <v>120</v>
       </c>
@@ -2791,7 +2791,7 @@
       <c r="X16" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y16" s="27"/>
+      <c r="Y16" s="23"/>
       <c r="Z16" s="8" t="s">
         <v>121</v>
       </c>
@@ -2810,7 +2810,7 @@
       <c r="AE16" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF16" s="27"/>
+      <c r="AF16" s="23"/>
       <c r="AG16" s="8" t="s">
         <v>120</v>
       </c>
@@ -2831,12 +2831,12 @@
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="AM16" s="21" t="s">
+      <c r="AM16" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="22"/>
-      <c r="AO16" s="22"/>
-      <c r="AP16" s="23"/>
+      <c r="AN16" s="25"/>
+      <c r="AO16" s="25"/>
+      <c r="AP16" s="26"/>
     </row>
     <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -2869,7 +2869,7 @@
       <c r="J17" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K17" s="27"/>
+      <c r="K17" s="23"/>
       <c r="L17" s="8" t="s">
         <v>120</v>
       </c>
@@ -2888,7 +2888,7 @@
       <c r="Q17" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R17" s="27"/>
+      <c r="R17" s="23"/>
       <c r="S17" s="8" t="s">
         <v>120</v>
       </c>
@@ -2907,7 +2907,7 @@
       <c r="X17" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y17" s="27"/>
+      <c r="Y17" s="23"/>
       <c r="Z17" s="8" t="s">
         <v>120</v>
       </c>
@@ -2926,7 +2926,7 @@
       <c r="AE17" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF17" s="27"/>
+      <c r="AF17" s="23"/>
       <c r="AG17" s="8" t="s">
         <v>120</v>
       </c>
@@ -2991,7 +2991,7 @@
       <c r="J18" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="23"/>
       <c r="L18" s="8" t="s">
         <v>120</v>
       </c>
@@ -3010,7 +3010,7 @@
       <c r="Q18" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R18" s="27"/>
+      <c r="R18" s="23"/>
       <c r="S18" s="8" t="s">
         <v>121</v>
       </c>
@@ -3029,7 +3029,7 @@
       <c r="X18" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y18" s="27"/>
+      <c r="Y18" s="23"/>
       <c r="Z18" s="8" t="s">
         <v>121</v>
       </c>
@@ -3048,7 +3048,7 @@
       <c r="AE18" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF18" s="27"/>
+      <c r="AF18" s="23"/>
       <c r="AG18" s="8" t="s">
         <v>121</v>
       </c>
@@ -3116,7 +3116,7 @@
       <c r="J19" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K19" s="27"/>
+      <c r="K19" s="23"/>
       <c r="L19" s="8" t="s">
         <v>121</v>
       </c>
@@ -3135,7 +3135,7 @@
       <c r="Q19" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R19" s="27"/>
+      <c r="R19" s="23"/>
       <c r="S19" s="8" t="s">
         <v>120</v>
       </c>
@@ -3154,7 +3154,7 @@
       <c r="X19" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="Y19" s="27"/>
+      <c r="Y19" s="23"/>
       <c r="Z19" s="8" t="s">
         <v>120</v>
       </c>
@@ -3173,7 +3173,7 @@
       <c r="AE19" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF19" s="27"/>
+      <c r="AF19" s="23"/>
       <c r="AG19" s="8" t="s">
         <v>120</v>
       </c>
@@ -3241,7 +3241,7 @@
       <c r="J20" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="K20" s="27"/>
+      <c r="K20" s="23"/>
       <c r="L20" s="8" t="s">
         <v>122</v>
       </c>
@@ -3260,7 +3260,7 @@
       <c r="Q20" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R20" s="27"/>
+      <c r="R20" s="23"/>
       <c r="S20" s="8" t="s">
         <v>121</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="X20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y20" s="27"/>
+      <c r="Y20" s="23"/>
       <c r="Z20" s="8" t="s">
         <v>121</v>
       </c>
@@ -3298,7 +3298,7 @@
       <c r="AE20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF20" s="27"/>
+      <c r="AF20" s="23"/>
       <c r="AG20" s="8" t="s">
         <v>120</v>
       </c>
@@ -3366,7 +3366,7 @@
       <c r="J21" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K21" s="27"/>
+      <c r="K21" s="23"/>
       <c r="L21" s="8" t="s">
         <v>120</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>120</v>
       </c>
       <c r="Q21" s="8"/>
-      <c r="R21" s="27"/>
+      <c r="R21" s="23"/>
       <c r="S21" s="8" t="s">
         <v>120</v>
       </c>
@@ -3402,7 +3402,7 @@
       <c r="X21" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y21" s="27"/>
+      <c r="Y21" s="23"/>
       <c r="Z21" s="8" t="s">
         <v>120</v>
       </c>
@@ -3421,7 +3421,7 @@
       <c r="AE21" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF21" s="27"/>
+      <c r="AF21" s="23"/>
       <c r="AG21" s="8" t="s">
         <v>120</v>
       </c>
@@ -3474,7 +3474,7 @@
       <c r="J22" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K22" s="27"/>
+      <c r="K22" s="23"/>
       <c r="L22" s="8" t="s">
         <v>120</v>
       </c>
@@ -3493,7 +3493,7 @@
       <c r="Q22" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R22" s="27"/>
+      <c r="R22" s="23"/>
       <c r="S22" s="8" t="s">
         <v>120</v>
       </c>
@@ -3512,7 +3512,7 @@
       <c r="X22" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y22" s="27"/>
+      <c r="Y22" s="23"/>
       <c r="Z22" s="8" t="s">
         <v>120</v>
       </c>
@@ -3531,7 +3531,7 @@
       <c r="AE22" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF22" s="27"/>
+      <c r="AF22" s="23"/>
       <c r="AG22" s="8" t="s">
         <v>120</v>
       </c>
@@ -3584,7 +3584,7 @@
       <c r="J23" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K23" s="27"/>
+      <c r="K23" s="23"/>
       <c r="L23" s="8" t="s">
         <v>120</v>
       </c>
@@ -3603,7 +3603,7 @@
       <c r="Q23" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R23" s="27"/>
+      <c r="R23" s="23"/>
       <c r="S23" s="8" t="s">
         <v>120</v>
       </c>
@@ -3622,7 +3622,7 @@
       <c r="X23" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y23" s="27"/>
+      <c r="Y23" s="23"/>
       <c r="Z23" s="8" t="s">
         <v>120</v>
       </c>
@@ -3641,7 +3641,7 @@
       <c r="AE23" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF23" s="27"/>
+      <c r="AF23" s="23"/>
       <c r="AG23" s="8" t="s">
         <v>120</v>
       </c>
@@ -3694,7 +3694,7 @@
       <c r="J24" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K24" s="27"/>
+      <c r="K24" s="23"/>
       <c r="L24" s="8" t="s">
         <v>120</v>
       </c>
@@ -3713,7 +3713,7 @@
       <c r="Q24" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R24" s="27"/>
+      <c r="R24" s="23"/>
       <c r="S24" s="8" t="s">
         <v>120</v>
       </c>
@@ -3732,7 +3732,7 @@
       <c r="X24" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y24" s="27"/>
+      <c r="Y24" s="23"/>
       <c r="Z24" s="8" t="s">
         <v>120</v>
       </c>
@@ -3751,7 +3751,7 @@
       <c r="AE24" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF24" s="27"/>
+      <c r="AF24" s="23"/>
       <c r="AG24" s="8" t="s">
         <v>120</v>
       </c>
@@ -3804,7 +3804,7 @@
       <c r="J25" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K25" s="27"/>
+      <c r="K25" s="23"/>
       <c r="L25" s="8" t="s">
         <v>120</v>
       </c>
@@ -3823,7 +3823,7 @@
       <c r="Q25" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R25" s="27"/>
+      <c r="R25" s="23"/>
       <c r="S25" s="8" t="s">
         <v>120</v>
       </c>
@@ -3842,7 +3842,7 @@
       <c r="X25" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="Y25" s="27"/>
+      <c r="Y25" s="23"/>
       <c r="Z25" s="8" t="s">
         <v>121</v>
       </c>
@@ -3861,7 +3861,7 @@
       <c r="AE25" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AF25" s="27"/>
+      <c r="AF25" s="23"/>
       <c r="AG25" s="8" t="s">
         <v>120</v>
       </c>
@@ -3914,7 +3914,7 @@
       <c r="J26" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K26" s="27"/>
+      <c r="K26" s="23"/>
       <c r="L26" s="8" t="s">
         <v>120</v>
       </c>
@@ -3933,7 +3933,7 @@
       <c r="Q26" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R26" s="27"/>
+      <c r="R26" s="23"/>
       <c r="S26" s="8" t="s">
         <v>120</v>
       </c>
@@ -3952,7 +3952,7 @@
       <c r="X26" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y26" s="27"/>
+      <c r="Y26" s="23"/>
       <c r="Z26" s="8" t="s">
         <v>120</v>
       </c>
@@ -3971,7 +3971,7 @@
       <c r="AE26" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF26" s="27"/>
+      <c r="AF26" s="23"/>
       <c r="AG26" s="8" t="s">
         <v>120</v>
       </c>
@@ -4024,7 +4024,7 @@
       <c r="J27" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K27" s="27"/>
+      <c r="K27" s="23"/>
       <c r="L27" s="8" t="s">
         <v>120</v>
       </c>
@@ -4043,7 +4043,7 @@
       <c r="Q27" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R27" s="27"/>
+      <c r="R27" s="23"/>
       <c r="S27" s="8" t="s">
         <v>120</v>
       </c>
@@ -4062,7 +4062,7 @@
       <c r="X27" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y27" s="27"/>
+      <c r="Y27" s="23"/>
       <c r="Z27" s="8" t="s">
         <v>120</v>
       </c>
@@ -4081,7 +4081,7 @@
       <c r="AE27" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF27" s="27"/>
+      <c r="AF27" s="23"/>
       <c r="AG27" s="8" t="s">
         <v>121</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="J28" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K28" s="27"/>
+      <c r="K28" s="23"/>
       <c r="L28" s="8" t="s">
         <v>120</v>
       </c>
@@ -4153,7 +4153,7 @@
       <c r="Q28" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R28" s="27"/>
+      <c r="R28" s="23"/>
       <c r="S28" s="8" t="s">
         <v>120</v>
       </c>
@@ -4172,7 +4172,7 @@
       <c r="X28" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y28" s="27"/>
+      <c r="Y28" s="23"/>
       <c r="Z28" s="8" t="s">
         <v>120</v>
       </c>
@@ -4191,7 +4191,7 @@
       <c r="AE28" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF28" s="27"/>
+      <c r="AF28" s="23"/>
       <c r="AG28" s="8" t="s">
         <v>120</v>
       </c>
@@ -4244,7 +4244,7 @@
       <c r="J29" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K29" s="27"/>
+      <c r="K29" s="23"/>
       <c r="L29" s="8" t="s">
         <v>120</v>
       </c>
@@ -4263,7 +4263,7 @@
       <c r="Q29" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R29" s="27"/>
+      <c r="R29" s="23"/>
       <c r="S29" s="8" t="s">
         <v>120</v>
       </c>
@@ -4282,7 +4282,7 @@
       <c r="X29" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y29" s="27"/>
+      <c r="Y29" s="23"/>
       <c r="Z29" s="8" t="s">
         <v>120</v>
       </c>
@@ -4301,7 +4301,7 @@
       <c r="AE29" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF29" s="27"/>
+      <c r="AF29" s="23"/>
       <c r="AG29" s="8" t="s">
         <v>120</v>
       </c>
@@ -4354,7 +4354,7 @@
       <c r="J30" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K30" s="27"/>
+      <c r="K30" s="23"/>
       <c r="L30" s="8" t="s">
         <v>120</v>
       </c>
@@ -4373,7 +4373,7 @@
       <c r="Q30" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R30" s="27"/>
+      <c r="R30" s="23"/>
       <c r="S30" s="8" t="s">
         <v>120</v>
       </c>
@@ -4392,7 +4392,7 @@
       <c r="X30" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y30" s="27"/>
+      <c r="Y30" s="23"/>
       <c r="Z30" s="8" t="s">
         <v>120</v>
       </c>
@@ -4411,7 +4411,7 @@
       <c r="AE30" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF30" s="27"/>
+      <c r="AF30" s="23"/>
       <c r="AG30" s="8" t="s">
         <v>120</v>
       </c>
@@ -4464,7 +4464,7 @@
       <c r="J31" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K31" s="27"/>
+      <c r="K31" s="23"/>
       <c r="L31" s="8" t="s">
         <v>120</v>
       </c>
@@ -4483,7 +4483,7 @@
       <c r="Q31" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R31" s="27"/>
+      <c r="R31" s="23"/>
       <c r="S31" s="8" t="s">
         <v>120</v>
       </c>
@@ -4502,7 +4502,7 @@
       <c r="X31" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y31" s="27"/>
+      <c r="Y31" s="23"/>
       <c r="Z31" s="8" t="s">
         <v>120</v>
       </c>
@@ -4521,7 +4521,7 @@
       <c r="AE31" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF31" s="27"/>
+      <c r="AF31" s="23"/>
       <c r="AG31" s="8" t="s">
         <v>120</v>
       </c>
@@ -4574,7 +4574,7 @@
       <c r="J32" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K32" s="27"/>
+      <c r="K32" s="23"/>
       <c r="L32" s="8" t="s">
         <v>120</v>
       </c>
@@ -4593,7 +4593,7 @@
       <c r="Q32" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R32" s="27"/>
+      <c r="R32" s="23"/>
       <c r="S32" s="8" t="s">
         <v>120</v>
       </c>
@@ -4612,7 +4612,7 @@
       <c r="X32" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y32" s="27"/>
+      <c r="Y32" s="23"/>
       <c r="Z32" s="8" t="s">
         <v>121</v>
       </c>
@@ -4631,7 +4631,7 @@
       <c r="AE32" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF32" s="27"/>
+      <c r="AF32" s="23"/>
       <c r="AG32" s="8" t="s">
         <v>120</v>
       </c>
@@ -4684,7 +4684,7 @@
       <c r="J33" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K33" s="27"/>
+      <c r="K33" s="23"/>
       <c r="L33" s="8" t="s">
         <v>120</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="Q33" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R33" s="27"/>
+      <c r="R33" s="23"/>
       <c r="S33" s="8" t="s">
         <v>120</v>
       </c>
@@ -4722,7 +4722,7 @@
       <c r="X33" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y33" s="27"/>
+      <c r="Y33" s="23"/>
       <c r="Z33" s="8" t="s">
         <v>120</v>
       </c>
@@ -4741,7 +4741,7 @@
       <c r="AE33" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF33" s="27"/>
+      <c r="AF33" s="23"/>
       <c r="AG33" s="8" t="s">
         <v>120</v>
       </c>
@@ -4794,7 +4794,7 @@
       <c r="J34" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K34" s="27"/>
+      <c r="K34" s="23"/>
       <c r="L34" s="8" t="s">
         <v>120</v>
       </c>
@@ -4813,7 +4813,7 @@
       <c r="Q34" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R34" s="27"/>
+      <c r="R34" s="23"/>
       <c r="S34" s="8" t="s">
         <v>120</v>
       </c>
@@ -4832,7 +4832,7 @@
       <c r="X34" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y34" s="27"/>
+      <c r="Y34" s="23"/>
       <c r="Z34" s="8" t="s">
         <v>120</v>
       </c>
@@ -4851,7 +4851,7 @@
       <c r="AE34" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF34" s="27"/>
+      <c r="AF34" s="23"/>
       <c r="AG34" s="8" t="s">
         <v>120</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>120</v>
       </c>
       <c r="J35" s="20"/>
-      <c r="K35" s="27"/>
+      <c r="K35" s="23"/>
       <c r="L35" s="8" t="s">
         <v>120</v>
       </c>
@@ -4921,7 +4921,7 @@
       <c r="Q35" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R35" s="27"/>
+      <c r="R35" s="23"/>
       <c r="S35" s="8" t="s">
         <v>121</v>
       </c>
@@ -4940,7 +4940,7 @@
       <c r="X35" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y35" s="27"/>
+      <c r="Y35" s="23"/>
       <c r="Z35" s="8" t="s">
         <v>120</v>
       </c>
@@ -4959,7 +4959,7 @@
       <c r="AE35" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF35" s="27"/>
+      <c r="AF35" s="23"/>
       <c r="AG35" s="8" t="s">
         <v>120</v>
       </c>
@@ -5012,7 +5012,7 @@
       <c r="J36" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K36" s="27"/>
+      <c r="K36" s="23"/>
       <c r="L36" s="8" t="s">
         <v>120</v>
       </c>
@@ -5031,7 +5031,7 @@
       <c r="Q36" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R36" s="27"/>
+      <c r="R36" s="23"/>
       <c r="S36" s="8" t="s">
         <v>120</v>
       </c>
@@ -5050,7 +5050,7 @@
       <c r="X36" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y36" s="27"/>
+      <c r="Y36" s="23"/>
       <c r="Z36" s="8" t="s">
         <v>120</v>
       </c>
@@ -5069,7 +5069,7 @@
       <c r="AE36" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF36" s="27"/>
+      <c r="AF36" s="23"/>
       <c r="AG36" s="8" t="s">
         <v>120</v>
       </c>
@@ -5122,7 +5122,7 @@
       <c r="J37" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K37" s="27"/>
+      <c r="K37" s="23"/>
       <c r="L37" s="8" t="s">
         <v>120</v>
       </c>
@@ -5141,7 +5141,7 @@
       <c r="Q37" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R37" s="27"/>
+      <c r="R37" s="23"/>
       <c r="S37" s="8" t="s">
         <v>121</v>
       </c>
@@ -5160,7 +5160,7 @@
       <c r="X37" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y37" s="27"/>
+      <c r="Y37" s="23"/>
       <c r="Z37" s="8" t="s">
         <v>120</v>
       </c>
@@ -5179,7 +5179,7 @@
       <c r="AE37" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF37" s="27"/>
+      <c r="AF37" s="23"/>
       <c r="AG37" s="8" t="s">
         <v>120</v>
       </c>
@@ -5232,7 +5232,7 @@
       <c r="J38" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K38" s="27"/>
+      <c r="K38" s="23"/>
       <c r="L38" s="8" t="s">
         <v>121</v>
       </c>
@@ -5251,7 +5251,7 @@
       <c r="Q38" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R38" s="27"/>
+      <c r="R38" s="23"/>
       <c r="S38" s="8" t="s">
         <v>120</v>
       </c>
@@ -5270,7 +5270,7 @@
       <c r="X38" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y38" s="27"/>
+      <c r="Y38" s="23"/>
       <c r="Z38" s="8" t="s">
         <v>120</v>
       </c>
@@ -5289,7 +5289,7 @@
       <c r="AE38" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF38" s="27"/>
+      <c r="AF38" s="23"/>
       <c r="AG38" s="8" t="s">
         <v>120</v>
       </c>
@@ -5342,7 +5342,7 @@
       <c r="J39" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K39" s="27"/>
+      <c r="K39" s="23"/>
       <c r="L39" s="8" t="s">
         <v>120</v>
       </c>
@@ -5361,7 +5361,7 @@
       <c r="Q39" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R39" s="27"/>
+      <c r="R39" s="23"/>
       <c r="S39" s="8" t="s">
         <v>120</v>
       </c>
@@ -5380,7 +5380,7 @@
       <c r="X39" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y39" s="27"/>
+      <c r="Y39" s="23"/>
       <c r="Z39" s="8" t="s">
         <v>120</v>
       </c>
@@ -5399,7 +5399,7 @@
       <c r="AE39" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF39" s="27"/>
+      <c r="AF39" s="23"/>
       <c r="AG39" s="8" t="s">
         <v>120</v>
       </c>
@@ -5452,7 +5452,7 @@
       <c r="J40" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K40" s="27"/>
+      <c r="K40" s="23"/>
       <c r="L40" s="8" t="s">
         <v>120</v>
       </c>
@@ -5471,7 +5471,7 @@
       <c r="Q40" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R40" s="27"/>
+      <c r="R40" s="23"/>
       <c r="S40" s="8" t="s">
         <v>120</v>
       </c>
@@ -5490,7 +5490,7 @@
       <c r="X40" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y40" s="27"/>
+      <c r="Y40" s="23"/>
       <c r="Z40" s="8" t="s">
         <v>120</v>
       </c>
@@ -5509,7 +5509,7 @@
       <c r="AE40" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF40" s="27"/>
+      <c r="AF40" s="23"/>
       <c r="AG40" s="8" t="s">
         <v>120</v>
       </c>
@@ -5560,7 +5560,7 @@
       <c r="J41" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K41" s="27"/>
+      <c r="K41" s="23"/>
       <c r="L41" s="8" t="s">
         <v>120</v>
       </c>
@@ -5579,7 +5579,7 @@
       <c r="Q41" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R41" s="27"/>
+      <c r="R41" s="23"/>
       <c r="S41" s="8" t="s">
         <v>120</v>
       </c>
@@ -5598,7 +5598,7 @@
       <c r="X41" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y41" s="27"/>
+      <c r="Y41" s="23"/>
       <c r="Z41" s="8" t="s">
         <v>120</v>
       </c>
@@ -5617,7 +5617,7 @@
       <c r="AE41" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF41" s="27"/>
+      <c r="AF41" s="23"/>
       <c r="AG41" s="8" t="s">
         <v>120</v>
       </c>
@@ -5670,7 +5670,7 @@
       <c r="J42" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K42" s="27"/>
+      <c r="K42" s="23"/>
       <c r="L42" s="8" t="s">
         <v>120</v>
       </c>
@@ -5689,7 +5689,7 @@
       <c r="Q42" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R42" s="27"/>
+      <c r="R42" s="23"/>
       <c r="S42" s="8" t="s">
         <v>120</v>
       </c>
@@ -5708,7 +5708,7 @@
       <c r="X42" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y42" s="27"/>
+      <c r="Y42" s="23"/>
       <c r="Z42" s="8" t="s">
         <v>120</v>
       </c>
@@ -5727,7 +5727,7 @@
       <c r="AE42" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF42" s="27"/>
+      <c r="AF42" s="23"/>
       <c r="AG42" s="8" t="s">
         <v>120</v>
       </c>
@@ -5780,7 +5780,7 @@
       <c r="J43" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K43" s="27"/>
+      <c r="K43" s="23"/>
       <c r="L43" s="8" t="s">
         <v>120</v>
       </c>
@@ -5799,7 +5799,7 @@
       <c r="Q43" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R43" s="27"/>
+      <c r="R43" s="23"/>
       <c r="S43" s="8" t="s">
         <v>120</v>
       </c>
@@ -5818,7 +5818,7 @@
       <c r="X43" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y43" s="27"/>
+      <c r="Y43" s="23"/>
       <c r="Z43" s="8" t="s">
         <v>120</v>
       </c>
@@ -5837,7 +5837,7 @@
       <c r="AE43" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF43" s="27"/>
+      <c r="AF43" s="23"/>
       <c r="AG43" s="8" t="s">
         <v>121</v>
       </c>
@@ -5890,7 +5890,7 @@
       <c r="J44" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K44" s="27"/>
+      <c r="K44" s="23"/>
       <c r="L44" s="8" t="s">
         <v>120</v>
       </c>
@@ -5909,7 +5909,7 @@
       <c r="Q44" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R44" s="27"/>
+      <c r="R44" s="23"/>
       <c r="S44" s="8" t="s">
         <v>120</v>
       </c>
@@ -5928,7 +5928,7 @@
       <c r="X44" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y44" s="27"/>
+      <c r="Y44" s="23"/>
       <c r="Z44" s="8" t="s">
         <v>120</v>
       </c>
@@ -5947,7 +5947,7 @@
       <c r="AE44" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF44" s="27"/>
+      <c r="AF44" s="23"/>
       <c r="AG44" s="8" t="s">
         <v>120</v>
       </c>
@@ -6000,7 +6000,7 @@
       <c r="J45" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K45" s="27"/>
+      <c r="K45" s="23"/>
       <c r="L45" s="8" t="s">
         <v>121</v>
       </c>
@@ -6019,7 +6019,7 @@
       <c r="Q45" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R45" s="27"/>
+      <c r="R45" s="23"/>
       <c r="S45" s="8" t="s">
         <v>120</v>
       </c>
@@ -6038,7 +6038,7 @@
       <c r="X45" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y45" s="27"/>
+      <c r="Y45" s="23"/>
       <c r="Z45" s="8" t="s">
         <v>121</v>
       </c>
@@ -6057,7 +6057,7 @@
       <c r="AE45" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF45" s="27"/>
+      <c r="AF45" s="23"/>
       <c r="AG45" s="8" t="s">
         <v>120</v>
       </c>
@@ -6110,7 +6110,7 @@
       <c r="J46" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K46" s="27"/>
+      <c r="K46" s="23"/>
       <c r="L46" s="8" t="s">
         <v>120</v>
       </c>
@@ -6129,7 +6129,7 @@
       <c r="Q46" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R46" s="27"/>
+      <c r="R46" s="23"/>
       <c r="S46" s="8" t="s">
         <v>120</v>
       </c>
@@ -6148,7 +6148,7 @@
       <c r="X46" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y46" s="27"/>
+      <c r="Y46" s="23"/>
       <c r="Z46" s="8" t="s">
         <v>120</v>
       </c>
@@ -6167,7 +6167,7 @@
       <c r="AE46" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF46" s="27"/>
+      <c r="AF46" s="23"/>
       <c r="AG46" s="8" t="s">
         <v>120</v>
       </c>
@@ -6218,7 +6218,7 @@
       <c r="J47" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K47" s="27"/>
+      <c r="K47" s="23"/>
       <c r="L47" s="8" t="s">
         <v>120</v>
       </c>
@@ -6237,7 +6237,7 @@
       <c r="Q47" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R47" s="27"/>
+      <c r="R47" s="23"/>
       <c r="S47" s="8" t="s">
         <v>120</v>
       </c>
@@ -6256,7 +6256,7 @@
       <c r="X47" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y47" s="27"/>
+      <c r="Y47" s="23"/>
       <c r="Z47" s="8" t="s">
         <v>120</v>
       </c>
@@ -6275,7 +6275,7 @@
       <c r="AE47" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF47" s="27"/>
+      <c r="AF47" s="23"/>
       <c r="AG47" s="8" t="s">
         <v>120</v>
       </c>
@@ -6328,7 +6328,7 @@
       <c r="J48" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K48" s="27"/>
+      <c r="K48" s="23"/>
       <c r="L48" s="8" t="s">
         <v>120</v>
       </c>
@@ -6347,7 +6347,7 @@
       <c r="Q48" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R48" s="27"/>
+      <c r="R48" s="23"/>
       <c r="S48" s="8" t="s">
         <v>120</v>
       </c>
@@ -6366,7 +6366,7 @@
       <c r="X48" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y48" s="27"/>
+      <c r="Y48" s="23"/>
       <c r="Z48" s="8" t="s">
         <v>120</v>
       </c>
@@ -6385,7 +6385,7 @@
       <c r="AE48" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF48" s="27"/>
+      <c r="AF48" s="23"/>
       <c r="AG48" s="8" t="s">
         <v>120</v>
       </c>
@@ -6436,7 +6436,7 @@
       <c r="J49" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K49" s="27"/>
+      <c r="K49" s="23"/>
       <c r="L49" s="8" t="s">
         <v>120</v>
       </c>
@@ -6455,7 +6455,7 @@
       <c r="Q49" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R49" s="27"/>
+      <c r="R49" s="23"/>
       <c r="S49" s="8" t="s">
         <v>120</v>
       </c>
@@ -6474,7 +6474,7 @@
       <c r="X49" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y49" s="27"/>
+      <c r="Y49" s="23"/>
       <c r="Z49" s="8" t="s">
         <v>120</v>
       </c>
@@ -6493,7 +6493,7 @@
       <c r="AE49" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF49" s="27"/>
+      <c r="AF49" s="23"/>
       <c r="AG49" s="8" t="s">
         <v>120</v>
       </c>
@@ -6544,7 +6544,7 @@
       <c r="J50" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K50" s="27"/>
+      <c r="K50" s="23"/>
       <c r="L50" s="8" t="s">
         <v>120</v>
       </c>
@@ -6563,7 +6563,7 @@
       <c r="Q50" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R50" s="27"/>
+      <c r="R50" s="23"/>
       <c r="S50" s="8" t="s">
         <v>121</v>
       </c>
@@ -6582,7 +6582,7 @@
       <c r="X50" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y50" s="27"/>
+      <c r="Y50" s="23"/>
       <c r="Z50" s="8" t="s">
         <v>120</v>
       </c>
@@ -6601,7 +6601,7 @@
       <c r="AE50" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF50" s="27"/>
+      <c r="AF50" s="23"/>
       <c r="AG50" s="8" t="s">
         <v>120</v>
       </c>
@@ -6652,7 +6652,7 @@
       <c r="J51" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K51" s="27"/>
+      <c r="K51" s="23"/>
       <c r="L51" s="8" t="s">
         <v>120</v>
       </c>
@@ -6671,7 +6671,7 @@
       <c r="Q51" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R51" s="27"/>
+      <c r="R51" s="23"/>
       <c r="S51" s="8" t="s">
         <v>120</v>
       </c>
@@ -6690,7 +6690,7 @@
       <c r="X51" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y51" s="27"/>
+      <c r="Y51" s="23"/>
       <c r="Z51" s="8" t="s">
         <v>120</v>
       </c>
@@ -6709,7 +6709,7 @@
       <c r="AE51" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF51" s="27"/>
+      <c r="AF51" s="23"/>
       <c r="AG51" s="8" t="s">
         <v>120</v>
       </c>
@@ -6760,7 +6760,7 @@
       <c r="J52" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K52" s="27"/>
+      <c r="K52" s="23"/>
       <c r="L52" s="8" t="s">
         <v>120</v>
       </c>
@@ -6779,7 +6779,7 @@
       <c r="Q52" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R52" s="27"/>
+      <c r="R52" s="23"/>
       <c r="S52" s="8" t="s">
         <v>120</v>
       </c>
@@ -6798,7 +6798,7 @@
       <c r="X52" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y52" s="27"/>
+      <c r="Y52" s="23"/>
       <c r="Z52" s="8" t="s">
         <v>120</v>
       </c>
@@ -6817,7 +6817,7 @@
       <c r="AE52" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF52" s="27"/>
+      <c r="AF52" s="23"/>
       <c r="AG52" s="8" t="s">
         <v>120</v>
       </c>
@@ -6868,7 +6868,7 @@
       <c r="J53" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="K53" s="27"/>
+      <c r="K53" s="23"/>
       <c r="L53" s="8" t="s">
         <v>120</v>
       </c>
@@ -6887,7 +6887,7 @@
       <c r="Q53" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R53" s="27"/>
+      <c r="R53" s="23"/>
       <c r="S53" s="8" t="s">
         <v>120</v>
       </c>
@@ -6906,7 +6906,7 @@
       <c r="X53" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="Y53" s="27"/>
+      <c r="Y53" s="23"/>
       <c r="Z53" s="8" t="s">
         <v>120</v>
       </c>
@@ -6925,7 +6925,7 @@
       <c r="AE53" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF53" s="27"/>
+      <c r="AF53" s="23"/>
       <c r="AG53" s="8" t="s">
         <v>120</v>
       </c>
@@ -6976,7 +6976,7 @@
       <c r="J54" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K54" s="27"/>
+      <c r="K54" s="23"/>
       <c r="L54" s="8" t="s">
         <v>120</v>
       </c>
@@ -6995,7 +6995,7 @@
       <c r="Q54" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R54" s="27"/>
+      <c r="R54" s="23"/>
       <c r="S54" s="8" t="s">
         <v>120</v>
       </c>
@@ -7014,7 +7014,7 @@
       <c r="X54" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y54" s="27"/>
+      <c r="Y54" s="23"/>
       <c r="Z54" s="8" t="s">
         <v>120</v>
       </c>
@@ -7033,7 +7033,7 @@
       <c r="AE54" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF54" s="27"/>
+      <c r="AF54" s="23"/>
       <c r="AG54" s="8" t="s">
         <v>120</v>
       </c>
@@ -7076,7 +7076,7 @@
       <c r="J55" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="K55" s="27"/>
+      <c r="K55" s="23"/>
       <c r="L55" s="8" t="s">
         <v>121</v>
       </c>
@@ -7095,7 +7095,7 @@
       <c r="Q55" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="R55" s="27"/>
+      <c r="R55" s="23"/>
       <c r="S55" s="8" t="s">
         <v>120</v>
       </c>
@@ -7114,7 +7114,7 @@
       <c r="X55" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="Y55" s="27"/>
+      <c r="Y55" s="23"/>
       <c r="Z55" s="8" t="s">
         <v>120</v>
       </c>
@@ -7133,7 +7133,7 @@
       <c r="AE55" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AF55" s="27"/>
+      <c r="AF55" s="23"/>
       <c r="AG55" s="8" t="s">
         <v>120</v>
       </c>
@@ -7172,7 +7172,7 @@
       <c r="H56" s="20"/>
       <c r="I56" s="20"/>
       <c r="J56" s="20"/>
-      <c r="K56" s="27"/>
+      <c r="K56" s="23"/>
       <c r="L56" s="8" t="s">
         <v>120</v>
       </c>
@@ -7191,7 +7191,7 @@
       <c r="Q56" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R56" s="27"/>
+      <c r="R56" s="23"/>
       <c r="S56" s="8" t="s">
         <v>121</v>
       </c>
@@ -7210,7 +7210,7 @@
       <c r="X56" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y56" s="27"/>
+      <c r="Y56" s="23"/>
       <c r="Z56" s="8" t="s">
         <v>120</v>
       </c>
@@ -7229,7 +7229,7 @@
       <c r="AE56" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF56" s="27"/>
+      <c r="AF56" s="23"/>
       <c r="AG56" s="8" t="s">
         <v>121</v>
       </c>
@@ -7253,12 +7253,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A1:AJ1"/>
-    <mergeCell ref="K5:K56"/>
-    <mergeCell ref="R5:R56"/>
-    <mergeCell ref="Y5:Y56"/>
-    <mergeCell ref="AF5:AF56"/>
     <mergeCell ref="AM16:AP16"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="AM3:AN3"/>
@@ -7269,25 +7263,29 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="K5:K56"/>
+    <mergeCell ref="R5:R56"/>
+    <mergeCell ref="Y5:Y56"/>
+    <mergeCell ref="AF5:AF56"/>
   </mergeCells>
+  <conditionalFormatting sqref="F3:AJ5 F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56 AM4:AN4">
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>F$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F4:AJ5 F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56">
-    <cfRule type="expression" dxfId="9" priority="15">
+    <cfRule type="expression" dxfId="8" priority="15">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:AJ5 F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM4:AN4 F3:AJ5 F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56">
-    <cfRule type="expression" dxfId="7" priority="16">
-      <formula>F$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AJ5 F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
-      <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AL3 AK5:AL56">
